--- a/Employee_Reports_wi52/Manuel Jr. Esplago Feniza Q0279.xlsx
+++ b/Employee_Reports_wi52/Manuel Jr. Esplago Feniza Q0279.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-11</v>
+        <v>-19</v>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -863,11 +863,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -900,11 +900,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -949,11 +949,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -998,11 +998,11 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-251</v>
+        <v>-259</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1047,11 +1047,11 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-155</v>
+        <v>-163</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1096,11 +1096,11 @@
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1124,20 +1124,20 @@
       <c r="E15" s="3" t="inlineStr"/>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>05-Jul-2025</t>
+          <t>25-Aug-2026</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>05-Jul-2027</t>
+          <t>24-Aug-2028</t>
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>319</v>
+        <v>727</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7601</v>
+        <v>7593</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
